--- a/exports/FORCEMOT_full_report.xlsx
+++ b/exports/FORCEMOT_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.47</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1315</v>
+        <v>1231.95</v>
       </c>
       <c r="I2" t="n">
         <v>1286.052485810823</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>3.74</v>
+        <v>-2.82</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>4.16</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3</v>
+        <v>0.76</v>
       </c>
       <c r="N2" t="n">
-        <v>2.11</v>
+        <v>7.11</v>
       </c>
       <c r="O2" t="n">
         <v>0.96</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.47</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44643.55208333334</v>
+        <v>44644.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>1074.65</v>
+        <v>1081</v>
       </c>
       <c r="I3" t="n">
         <v>1075.668727160337</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K3" t="n">
-        <v>12.77</v>
+        <v>12.25</v>
       </c>
       <c r="L3" t="n">
         <v>6.83</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>6.68</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44649.38541666666</v>
+        <v>44649.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>1044.5</v>
+        <v>1009</v>
       </c>
       <c r="I4" t="n">
         <v>1018.738849803837</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.38</v>
+        <v>-6.66</v>
       </c>
       <c r="L4" t="n">
-        <v>4.72</v>
+        <v>6.75</v>
       </c>
       <c r="M4" t="n">
         <v>1.36</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>8.66</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44652.55208333334</v>
+        <v>44655.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1092</v>
+        <v>1111.5</v>
       </c>
       <c r="I5" t="n">
         <v>1096.343627329333</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>-8.23</v>
+        <v>-10.16</v>
       </c>
       <c r="L5" t="n">
-        <v>10.3</v>
+        <v>11.5</v>
       </c>
       <c r="M5" t="n">
         <v>2.08</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44686.55208333334</v>
+        <v>44687.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>1118.15</v>
+        <v>1072.25</v>
       </c>
       <c r="I6" t="n">
         <v>1098.502560375259</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6</v>
+        <v>-3.53</v>
       </c>
       <c r="L6" t="n">
-        <v>3.22</v>
+        <v>4.18</v>
       </c>
       <c r="M6" t="n">
-        <v>1.84</v>
+        <v>3.05</v>
       </c>
       <c r="N6" t="n">
-        <v>2.96</v>
+        <v>4.32</v>
       </c>
       <c r="O6" t="n">
         <v>3.21</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>10.64</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44739.55208333334</v>
+        <v>44740.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>938</v>
+        <v>1039.9</v>
       </c>
       <c r="I7" t="n">
         <v>994.2980203973556</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K7" t="n">
-        <v>12.52</v>
+        <v>3.02</v>
       </c>
       <c r="L7" t="n">
         <v>6.77</v>
@@ -840,7 +923,7 @@
         <v>2.49</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>13.75</v>
       </c>
       <c r="O7" t="n">
         <v>-4.32</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>12.54</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44827.55208333334</v>
+        <v>44830.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>1320</v>
+        <v>1246.4</v>
       </c>
       <c r="I8" t="n">
         <v>1289.205628902131</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>87.16666666666667</v>
+        <v>90</v>
       </c>
       <c r="K8" t="n">
-        <v>26.94</v>
+        <v>19.86</v>
       </c>
       <c r="L8" t="n">
         <v>9.710000000000001</v>
@@ -897,7 +992,7 @@
         <v>3.24</v>
       </c>
       <c r="N8" t="n">
-        <v>3.56</v>
+        <v>7.27</v>
       </c>
       <c r="O8" t="n">
         <v>13.75</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>12.03</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44847.38541666666</v>
+        <v>44847.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>1281.8</v>
+        <v>1342</v>
       </c>
       <c r="I9" t="n">
         <v>1326.252544576381</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.84</v>
+        <v>-7.67</v>
       </c>
       <c r="L9" t="n">
-        <v>5.26</v>
+        <v>7.88</v>
       </c>
       <c r="M9" t="n">
         <v>1.64</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>10.23</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44855.38541666666</v>
+        <v>44855.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>1319</v>
+        <v>1242.1</v>
       </c>
       <c r="I10" t="n">
         <v>1265.138453766763</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.71</v>
+        <v>-7.44</v>
       </c>
       <c r="L10" t="n">
-        <v>4.59</v>
+        <v>7.88</v>
       </c>
       <c r="M10" t="n">
         <v>0.52</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>11.65</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44868.55208333334</v>
+        <v>44869.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1366.5</v>
+        <v>1379.55</v>
       </c>
       <c r="I11" t="n">
         <v>1375.174834154308</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-10.02</v>
+        <v>-11.07</v>
       </c>
       <c r="L11" t="n">
-        <v>11.75</v>
+        <v>13.23</v>
       </c>
       <c r="M11" t="n">
         <v>1.44</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.54</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44904.55208333334</v>
+        <v>44907.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1489</v>
+        <v>1460.45</v>
       </c>
       <c r="I12" t="n">
         <v>1465.357807846997</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K12" t="n">
-        <v>7.93</v>
+        <v>5.86</v>
       </c>
       <c r="L12" t="n">
         <v>4.82</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.42</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44928.38541666666</v>
+        <v>44928.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>1442</v>
+        <v>1480</v>
       </c>
       <c r="I13" t="n">
         <v>1448.052451131985</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>1.26</v>
+        <v>-1.34</v>
       </c>
       <c r="L13" t="n">
         <v>5.1</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.31</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44950.38541666666</v>
+        <v>44950.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>1479.1</v>
+        <v>1470</v>
       </c>
       <c r="I14" t="n">
         <v>1470.33794894812</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>21.83333333333333</v>
+        <v>22</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.06</v>
+        <v>-0.68</v>
       </c>
       <c r="L14" t="n">
         <v>2.7</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.36</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44988.55208333334</v>
+        <v>44991.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>1251</v>
+        <v>1288.05</v>
       </c>
       <c r="I15" t="n">
         <v>1286.334175553116</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>38</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K15" t="n">
-        <v>14.9</v>
+        <v>12.38</v>
       </c>
       <c r="L15" t="n">
         <v>1.73</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.96</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45001.55208333334</v>
+        <v>45002.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1224</v>
+        <v>1205.35</v>
       </c>
       <c r="I16" t="n">
         <v>1213.141524282115</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.97</v>
+        <v>-6.42</v>
       </c>
       <c r="L16" t="n">
         <v>6.96</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45016.55208333334</v>
+        <v>45019.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>1180</v>
+        <v>1219.8</v>
       </c>
       <c r="I17" t="n">
         <v>1181.271567590299</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1</v>
+        <v>-1.2</v>
       </c>
       <c r="L17" t="n">
         <v>2.87</v>
@@ -1410,7 +1613,7 @@
         <v>1.4</v>
       </c>
       <c r="N17" t="n">
-        <v>4.04</v>
+        <v>5.08</v>
       </c>
       <c r="O17" t="n">
         <v>-0.9</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.31</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45134.38541666666</v>
+        <v>45134.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>2568.15</v>
+        <v>2547.4</v>
       </c>
       <c r="I18" t="n">
         <v>2551.748215669751</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>115</v>
+        <v>115.1666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>110.54</v>
+        <v>108.84</v>
       </c>
       <c r="L18" t="n">
         <v>4.41</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>157</v>
+        <v>158</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>6.98</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45142.38541666666</v>
+        <v>45142.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>2609.8</v>
+        <v>2694</v>
       </c>
       <c r="I19" t="n">
         <v>2668.888705559097</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.45</v>
+        <v>-5.75</v>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>5.95</v>
       </c>
       <c r="M19" t="n">
         <v>1.48</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>10.29</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45180.55208333334</v>
+        <v>45181.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>3815</v>
+        <v>3646</v>
       </c>
       <c r="I20" t="n">
         <v>3651.135071412918</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>38</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K20" t="n">
-        <v>41.61</v>
+        <v>35.34</v>
       </c>
       <c r="L20" t="n">
         <v>3.74</v>
@@ -1581,7 +1820,7 @@
         <v>0.63</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>4.43</v>
       </c>
       <c r="O20" t="n">
         <v>7.85</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>12.35</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45194.55208333334</v>
+        <v>45195.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>3758</v>
+        <v>3928</v>
       </c>
       <c r="I21" t="n">
         <v>3919.927397163801</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.07</v>
+        <v>-7.73</v>
       </c>
       <c r="L21" t="n">
-        <v>6.11</v>
+        <v>7.93</v>
       </c>
       <c r="M21" t="n">
         <v>1.74</v>
       </c>
       <c r="N21" t="n">
-        <v>2.83</v>
+        <v>4.72</v>
       </c>
       <c r="O21" t="n">
         <v>-4.43</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>9.57</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45216.55208333334</v>
+        <v>45217.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>3809.95</v>
+        <v>3755.9</v>
       </c>
       <c r="I22" t="n">
         <v>3780.832323467972</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.01</v>
+        <v>-4.38</v>
       </c>
       <c r="L22" t="n">
-        <v>4.8</v>
+        <v>5.17</v>
       </c>
       <c r="M22" t="n">
         <v>1.35</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>7.43</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45224.55208333334</v>
+        <v>45336.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>3352.35</v>
+        <v>4520</v>
       </c>
       <c r="I23" t="n">
         <v>3613.818501966456</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>119</v>
       </c>
       <c r="K23" t="n">
-        <v>10.74</v>
+        <v>-20.34</v>
       </c>
       <c r="L23" t="n">
-        <v>2.37</v>
+        <v>22.13</v>
       </c>
       <c r="M23" t="n">
-        <v>0.39</v>
+        <v>31.25</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>31.46</v>
       </c>
       <c r="O23" t="n">
         <v>-0.71</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45224</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>15.65</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45356.55208333334</v>
+        <v>45357.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>6450</v>
+        <v>6021.5</v>
       </c>
       <c r="I24" t="n">
         <v>6112.967688995805</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K24" t="n">
-        <v>42.7</v>
+        <v>33.22</v>
       </c>
       <c r="L24" t="n">
         <v>5.97</v>
@@ -1809,7 +2096,7 @@
         <v>2.83</v>
       </c>
       <c r="N24" t="n">
-        <v>5.88</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="O24" t="n">
         <v>31.46</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>14.98</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45366.55208333334</v>
+        <v>45369.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>6520</v>
+        <v>7024.3</v>
       </c>
       <c r="I25" t="n">
         <v>6743.519279092379</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K25" t="n">
-        <v>-8.279999999999999</v>
+        <v>-16.65</v>
       </c>
       <c r="L25" t="n">
-        <v>14.59</v>
+        <v>17.08</v>
       </c>
       <c r="M25" t="n">
         <v>1.11</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>17.41</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45421.55208333334</v>
+        <v>45422.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>9111</v>
+        <v>8961.200000000001</v>
       </c>
       <c r="I26" t="n">
         <v>9007.386154838108</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K26" t="n">
-        <v>29.71</v>
+        <v>27.57</v>
       </c>
       <c r="L26" t="n">
         <v>6.77</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>11.99</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45443.38541666666</v>
+        <v>45443.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>8392.5</v>
+        <v>8790</v>
       </c>
       <c r="I27" t="n">
         <v>8767.379398092653</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>6.35</v>
+        <v>1.91</v>
       </c>
       <c r="L27" t="n">
         <v>4.55</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>10.22</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>8920</v>
+        <v>8216.9</v>
       </c>
       <c r="I28" t="n">
         <v>8248.548084581076</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>1.48</v>
+        <v>-6.52</v>
       </c>
       <c r="L28" t="n">
-        <v>4.79</v>
+        <v>18.82</v>
       </c>
       <c r="M28" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>6.96</v>
       </c>
       <c r="O28" t="n">
         <v>3.53</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>12.01</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45467.38541666666</v>
+        <v>45467.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>9078.85</v>
+        <v>9380</v>
       </c>
       <c r="I29" t="n">
         <v>9203.626723877031</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>-10.49</v>
+        <v>-14.15</v>
       </c>
       <c r="L29" t="n">
-        <v>13.79</v>
+        <v>14.82</v>
       </c>
       <c r="M29" t="n">
         <v>1.15</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45477.55208333334</v>
+        <v>45478.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>8774.9</v>
+        <v>8538.049999999999</v>
       </c>
       <c r="I30" t="n">
         <v>8679.600245642321</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>-6.45</v>
+        <v>-8.98</v>
       </c>
       <c r="L30" t="n">
-        <v>6.77</v>
+        <v>9.15</v>
       </c>
       <c r="M30" t="n">
         <v>2.09</v>
       </c>
       <c r="N30" t="n">
-        <v>2.35</v>
+        <v>2.96</v>
       </c>
       <c r="O30" t="n">
         <v>5.61</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>8.4</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45499.55208333334</v>
+        <v>45502.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>8460</v>
+        <v>8756.6</v>
       </c>
       <c r="I31" t="n">
         <v>8627.540822775769</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K31" t="n">
-        <v>0.91</v>
+        <v>-2.56</v>
       </c>
       <c r="L31" t="n">
         <v>2.98</v>
@@ -2208,7 +2579,7 @@
         <v>1.56</v>
       </c>
       <c r="N31" t="n">
-        <v>3.17</v>
+        <v>3.49</v>
       </c>
       <c r="O31" t="n">
         <v>-2.96</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>7.24</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>9030</v>
+        <v>8507.9</v>
       </c>
       <c r="I32" t="n">
         <v>8613.134469969933</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K32" t="n">
-        <v>3.12</v>
+        <v>-2.84</v>
       </c>
       <c r="L32" t="n">
-        <v>2.35</v>
+        <v>3.55</v>
       </c>
       <c r="M32" t="n">
-        <v>1.14</v>
+        <v>4.1</v>
       </c>
       <c r="N32" t="n">
-        <v>1.97</v>
+        <v>5.99</v>
       </c>
       <c r="O32" t="n">
         <v>3.49</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>10.82</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45526.55208333334</v>
+        <v>45527.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>8650</v>
+        <v>8851.35</v>
       </c>
       <c r="I33" t="n">
         <v>8735.717607227209</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.67</v>
+        <v>-4.04</v>
       </c>
       <c r="L33" t="n">
-        <v>4.14</v>
+        <v>4.91</v>
       </c>
       <c r="M33" t="n">
         <v>1.9</v>
       </c>
       <c r="N33" t="n">
-        <v>2.22</v>
+        <v>3.21</v>
       </c>
       <c r="O33" t="n">
         <v>-5.99</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>7.24</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45531.38541666666</v>
+        <v>45531.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>8422.85</v>
+        <v>8380</v>
       </c>
       <c r="I34" t="n">
         <v>8390.369775601057</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.84</v>
+        <v>-5.33</v>
       </c>
       <c r="L34" t="n">
-        <v>5.14</v>
+        <v>5.63</v>
       </c>
       <c r="M34" t="n">
         <v>-0</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>6.94</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45554.55208333334</v>
+        <v>45555.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>6775</v>
+        <v>7230</v>
       </c>
       <c r="I35" t="n">
         <v>7218.143487630737</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>19.15</v>
+        <v>13.72</v>
       </c>
       <c r="L35" t="n">
         <v>2.17</v>
@@ -2436,7 +2855,7 @@
         <v>1.91</v>
       </c>
       <c r="N35" t="n">
-        <v>2.16</v>
+        <v>5.54</v>
       </c>
       <c r="O35" t="n">
         <v>-2.24</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.84</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>7200</v>
+        <v>6918.3</v>
       </c>
       <c r="I36" t="n">
         <v>6957.735685513501</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.41</v>
+        <v>-4.31</v>
       </c>
       <c r="L36" t="n">
         <v>6.78</v>
@@ -2493,7 +2924,7 @@
         <v>0.54</v>
       </c>
       <c r="N36" t="n">
-        <v>2.69</v>
+        <v>3.75</v>
       </c>
       <c r="O36" t="n">
         <v>5.54</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>13.49</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45594.55208333334</v>
+        <v>45595.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>6383.8</v>
+        <v>7661.9</v>
       </c>
       <c r="I37" t="n">
         <v>6760.741192917156</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K37" t="n">
-        <v>7.73</v>
+        <v>-10.75</v>
       </c>
       <c r="L37" t="n">
-        <v>6.54</v>
+        <v>10.75</v>
       </c>
       <c r="M37" t="n">
-        <v>1.77</v>
+        <v>13.16</v>
       </c>
       <c r="N37" t="n">
-        <v>4.18</v>
+        <v>20.02</v>
       </c>
       <c r="O37" t="n">
         <v>-3.75</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>15.3</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45607.38541666666</v>
+        <v>45607.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>7105.45</v>
+        <v>6995</v>
       </c>
       <c r="I38" t="n">
         <v>7088.824146789793</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>-7.26</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>8.140000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="M38" t="n">
         <v>0.24</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>10.65</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>6628</v>
+        <v>7194.95</v>
       </c>
       <c r="I39" t="n">
         <v>6817.513699396577</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>51</v>
+        <v>51.83333333333334</v>
       </c>
       <c r="K39" t="n">
-        <v>5.25</v>
+        <v>-2.86</v>
       </c>
       <c r="L39" t="n">
-        <v>2.2</v>
+        <v>3.43</v>
       </c>
       <c r="M39" t="n">
         <v>2.12</v>
       </c>
       <c r="N39" t="n">
-        <v>3.85</v>
+        <v>8.34</v>
       </c>
       <c r="O39" t="n">
         <v>-4.7</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.51</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45665.55208333334</v>
+        <v>45666.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>6870</v>
+        <v>6689.6</v>
       </c>
       <c r="I40" t="n">
         <v>6744.884386528984</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.52</v>
+        <v>-7.02</v>
       </c>
       <c r="L40" t="n">
         <v>7.96</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>10.44</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45692.55208333334</v>
+        <v>45693.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>6412</v>
+        <v>6781.95</v>
       </c>
       <c r="I41" t="n">
         <v>6721.75683788377</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K41" t="n">
-        <v>4.15</v>
+        <v>-1.38</v>
       </c>
       <c r="L41" t="n">
-        <v>3.4</v>
+        <v>5.37</v>
       </c>
       <c r="M41" t="n">
         <v>0.93</v>
       </c>
       <c r="N41" t="n">
-        <v>2.98</v>
+        <v>5.72</v>
       </c>
       <c r="O41" t="n">
         <v>-4.44</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>9.07</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45729.55208333334</v>
+        <v>45733.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>7261</v>
+        <v>7037.05</v>
       </c>
       <c r="I42" t="n">
         <v>7109.055101736056</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K42" t="n">
-        <v>7.06</v>
+        <v>3.76</v>
       </c>
       <c r="L42" t="n">
         <v>8.57</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>10.96</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>7460.05</v>
+        <v>7729</v>
       </c>
       <c r="I43" t="n">
         <v>7697.590325074322</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>-6.01</v>
+        <v>-9.83</v>
       </c>
       <c r="L43" t="n">
-        <v>6.29</v>
+        <v>9.83</v>
       </c>
       <c r="M43" t="n">
         <v>0.41</v>
       </c>
       <c r="N43" t="n">
-        <v>4.86</v>
+        <v>6.42</v>
       </c>
       <c r="O43" t="n">
         <v>-2.02</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>10.38</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>8852.799999999999</v>
+        <v>8123.5</v>
       </c>
       <c r="I44" t="n">
         <v>8418.216719760738</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>14.54</v>
+        <v>5.1</v>
       </c>
       <c r="L44" t="n">
         <v>3.98</v>
       </c>
       <c r="M44" t="n">
-        <v>0.68</v>
+        <v>9.07</v>
       </c>
       <c r="N44" t="n">
-        <v>2.77</v>
+        <v>6.07</v>
       </c>
       <c r="O44" t="n">
         <v>6.42</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>12.21</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45764.55208333334</v>
+        <v>45768.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>8721.5</v>
+        <v>9229.5</v>
       </c>
       <c r="I45" t="n">
         <v>9115.150002664979</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.36</v>
+        <v>-13.61</v>
       </c>
       <c r="L45" t="n">
-        <v>10.14</v>
+        <v>14.09</v>
       </c>
       <c r="M45" t="n">
         <v>3.22</v>
       </c>
       <c r="N45" t="n">
-        <v>3.12</v>
+        <v>7.1</v>
       </c>
       <c r="O45" t="n">
         <v>-6.07</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.67</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45840.55208333334</v>
+        <v>45841.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>14591</v>
+        <v>14402</v>
       </c>
       <c r="I46" t="n">
         <v>14458.02232784813</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>72.16666666666667</v>
+        <v>73</v>
       </c>
       <c r="K46" t="n">
-        <v>58.09</v>
+        <v>56.04</v>
       </c>
       <c r="L46" t="n">
         <v>5.63</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>12.47</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45846.55208333334</v>
+        <v>45847.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>15200</v>
+        <v>17037</v>
       </c>
       <c r="I47" t="n">
         <v>15663.36074308851</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K47" t="n">
-        <v>-5.54</v>
+        <v>-18.3</v>
       </c>
       <c r="L47" t="n">
-        <v>6.24</v>
+        <v>18.3</v>
       </c>
       <c r="M47" t="n">
         <v>1.41</v>
       </c>
       <c r="N47" t="n">
-        <v>3.33</v>
+        <v>10.03</v>
       </c>
       <c r="O47" t="n">
         <v>-1.51</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>15.56</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45869.38541666666</v>
+        <v>45869.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>17261</v>
+        <v>16964</v>
       </c>
       <c r="I48" t="n">
         <v>17229.24963445992</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>1.31</v>
+        <v>-0.43</v>
       </c>
       <c r="L48" t="n">
         <v>10.92</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>12.88</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45880.55208333334</v>
+        <v>45881.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>18602</v>
+        <v>18869</v>
       </c>
       <c r="I49" t="n">
         <v>18684.84960729287</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>-9.66</v>
+        <v>-11.23</v>
       </c>
       <c r="L49" t="n">
-        <v>9.94</v>
+        <v>11.85</v>
       </c>
       <c r="M49" t="n">
         <v>0.59</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45894.55208333334</v>
+        <v>45895.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>20150</v>
+        <v>19893</v>
       </c>
       <c r="I50" t="n">
         <v>20024.92840377664</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K50" t="n">
-        <v>6.79</v>
+        <v>5.43</v>
       </c>
       <c r="L50" t="n">
         <v>1.43</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>9.77</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45915.55208333334</v>
+        <v>45916.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>18750</v>
+        <v>19884</v>
       </c>
       <c r="I51" t="n">
         <v>19064.92588209567</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K51" t="n">
-        <v>5.75</v>
+        <v>0.05</v>
       </c>
       <c r="L51" t="n">
         <v>2.02</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>11.43</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45924.55208333334</v>
+        <v>45925.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>18096</v>
+        <v>17874</v>
       </c>
       <c r="I52" t="n">
         <v>18088.23270740175</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K52" t="n">
-        <v>-8.99</v>
+        <v>-10.11</v>
       </c>
       <c r="L52" t="n">
-        <v>10.23</v>
+        <v>10.48</v>
       </c>
       <c r="M52" t="n">
         <v>1.12</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45943.55208333334</v>
+        <v>45944.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>16111</v>
+        <v>16736</v>
       </c>
       <c r="I53" t="n">
         <v>16516.40058254035</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K53" t="n">
-        <v>9.859999999999999</v>
+        <v>6.37</v>
       </c>
       <c r="L53" t="n">
         <v>2.13</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>10.9</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45957.38541666666</v>
+        <v>45957.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>16324</v>
+        <v>16270</v>
       </c>
       <c r="I54" t="n">
         <v>16281.07813938876</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.46</v>
+        <v>-2.78</v>
       </c>
       <c r="L54" t="n">
         <v>4.51</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>8.74</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45960.55208333334</v>
+        <v>45961.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>17260</v>
+        <v>17650</v>
       </c>
       <c r="I55" t="n">
         <v>17628.48670322259</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-6.08</v>
+        <v>-8.48</v>
       </c>
       <c r="L55" t="n">
-        <v>6.18</v>
+        <v>9.83</v>
       </c>
       <c r="M55" t="n">
         <v>0.43</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>8.19</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45982.38541666666</v>
+        <v>45982.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>17193</v>
+        <v>16888</v>
       </c>
       <c r="I56" t="n">
         <v>17107.5123962664</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.59</v>
+        <v>-4.32</v>
       </c>
       <c r="L56" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="M56" t="n">
         <v>0.64</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>7.1</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45988.55208333334</v>
+        <v>45989.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>17248</v>
+        <v>17835</v>
       </c>
       <c r="I57" t="n">
         <v>17688.06874220899</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.13</v>
+        <v>-5.61</v>
       </c>
       <c r="L57" t="n">
-        <v>3.46</v>
+        <v>6.16</v>
       </c>
       <c r="M57" t="n">
         <v>0.89</v>
       </c>
       <c r="N57" t="n">
-        <v>1.89</v>
+        <v>3.03</v>
       </c>
       <c r="O57" t="n">
         <v>-3.3</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>7.61</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45995.55208333334</v>
+        <v>45996.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>17570</v>
+        <v>17177</v>
       </c>
       <c r="I58" t="n">
         <v>17179.03390610078</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.49</v>
+        <v>-3.69</v>
       </c>
       <c r="L58" t="n">
-        <v>3.67</v>
+        <v>4.29</v>
       </c>
       <c r="M58" t="n">
         <v>0.24</v>
       </c>
       <c r="N58" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="O58" t="n">
         <v>3.03</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.9</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46010.38541666666</v>
+        <v>46010.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>17732</v>
+        <v>17970</v>
       </c>
       <c r="I59" t="n">
         <v>17772.43672032807</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.23</v>
+        <v>-4.62</v>
       </c>
       <c r="L59" t="n">
         <v>6.21</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>20000</v>
+        <v>19300</v>
       </c>
       <c r="I60" t="n">
         <v>19604.40690975922</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K60" t="n">
-        <v>11.3</v>
+        <v>7.4</v>
       </c>
       <c r="L60" t="n">
         <v>2.95</v>
@@ -3861,7 +4580,7 @@
         <v>0.31</v>
       </c>
       <c r="N60" t="n">
-        <v>2.82</v>
+        <v>6.8</v>
       </c>
       <c r="O60" t="n">
         <v>3.86</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46038.55208333334</v>
+        <v>46041.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>20535</v>
+        <v>21275</v>
       </c>
       <c r="I61" t="n">
         <v>20658.33629040749</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K61" t="n">
-        <v>-6.4</v>
+        <v>-10.23</v>
       </c>
       <c r="L61" t="n">
-        <v>7.31</v>
+        <v>10.83</v>
       </c>
       <c r="M61" t="n">
         <v>0.61</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>10</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46045.38541666666</v>
+        <v>46045.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>19900</v>
+        <v>19340</v>
       </c>
       <c r="I62" t="n">
         <v>19474.56193636849</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-6.46</v>
+        <v>-9.1</v>
       </c>
       <c r="L62" t="n">
-        <v>8.859999999999999</v>
+        <v>10.69</v>
       </c>
       <c r="M62" t="n">
         <v>0.17</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>11.68</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46057.55208333334</v>
+        <v>46058.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>20158</v>
+        <v>21179</v>
       </c>
       <c r="I63" t="n">
         <v>20432.11144813791</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>-4.23</v>
+        <v>-9.51</v>
       </c>
       <c r="L63" t="n">
-        <v>4.78</v>
+        <v>14.79</v>
       </c>
       <c r="M63" t="n">
         <v>3.11</v>
       </c>
       <c r="N63" t="n">
-        <v>3.97</v>
+        <v>4.38</v>
       </c>
       <c r="O63" t="n">
         <v>-6.62</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,25 +4835,25 @@
         <v>10.17</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>24331</v>
+        <v>23305</v>
       </c>
       <c r="I64" t="n">
         <v>23556.53489977488</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K64" t="n">
-        <v>14.88</v>
+        <v>10.04</v>
       </c>
       <c r="L64" t="n">
         <v>3.21</v>
       </c>
       <c r="M64" t="n">
-        <v>0.88</v>
+        <v>5.06</v>
       </c>
       <c r="N64" t="n">
         <v>4.3</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>11.21</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46120.38541666666</v>
+        <v>46120.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>21650</v>
+        <v>22134</v>
       </c>
       <c r="I65" t="n">
         <v>21676.20105424318</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>37</v>
+        <v>37.16666666666666</v>
       </c>
       <c r="K65" t="n">
-        <v>7.1</v>
+        <v>5.02</v>
       </c>
       <c r="L65" t="n">
         <v>4.38</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>12.5</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46135.55208333334</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>20766</v>
+        <v>20249</v>
       </c>
       <c r="I66" t="n">
         <v>20462.44492108068</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K66" t="n">
-        <v>-6.18</v>
+        <v>-8.52</v>
       </c>
       <c r="L66" t="n">
-        <v>6.66</v>
+        <v>9.84</v>
       </c>
       <c r="M66" t="n">
         <v>3.37</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>10.03</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46148.55208333334</v>
+        <v>46149.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>20250</v>
+        <v>20950</v>
       </c>
       <c r="I67" t="n">
         <v>20846.38380730485</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K67" t="n">
-        <v>-0</v>
+        <v>-3.46</v>
       </c>
       <c r="L67" t="n">
         <v>5.98</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>11.86</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46174.38541666666</v>
+        <v>46174.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>19012</v>
+        <v>18990</v>
       </c>
       <c r="I68" t="n">
         <v>19011.7074310621</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K68" t="n">
-        <v>-9.25</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="L68" t="n">
         <v>10.36</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,25 +5180,25 @@
         <v>7.19</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>17855</v>
+        <v>18659</v>
       </c>
       <c r="I69" t="n">
         <v>18383.50684543827</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K69" t="n">
-        <v>5.98</v>
+        <v>1.74</v>
       </c>
       <c r="L69" t="n">
-        <v>0.49</v>
+        <v>1.11</v>
       </c>
       <c r="M69" t="n">
-        <v>2.55</v>
+        <v>3.04</v>
       </c>
       <c r="N69" t="n">
         <v>6.21</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>8.75</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46216.55208333334</v>
+        <v>46217.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>17980</v>
+        <v>17743</v>
       </c>
       <c r="I70" t="n">
         <v>17765.09188456613</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.64</v>
+        <v>-4.91</v>
       </c>
       <c r="L70" t="n">
-        <v>5.04</v>
+        <v>5.38</v>
       </c>
       <c r="M70" t="n">
         <v>1.12</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,25 +5318,25 @@
         <v>6.4</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46234.55208333334</v>
+        <v>46237.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>17870</v>
+        <v>18344</v>
       </c>
       <c r="I71" t="n">
         <v>18255.04259474722</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.72</v>
+        <v>-3.39</v>
       </c>
       <c r="L71" t="n">
         <v>5.53</v>
       </c>
       <c r="M71" t="n">
-        <v>1.14</v>
+        <v>1.94</v>
       </c>
       <c r="N71" t="n">
         <v>4.8</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>6.84</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46252.55208333334</v>
+        <v>46253.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>18251</v>
+        <v>17818</v>
       </c>
       <c r="I72" t="n">
         <v>18058.77053714986</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.51</v>
+        <v>-2.87</v>
       </c>
       <c r="L72" t="n">
-        <v>1.43</v>
+        <v>3.41</v>
       </c>
       <c r="M72" t="n">
         <v>0.59</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>7.6</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46274.55208333334</v>
+        <v>46275.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>17351</v>
+        <v>18027</v>
       </c>
       <c r="I73" t="n">
         <v>17992.2702419092</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K73" t="n">
-        <v>2.62</v>
+        <v>-1.17</v>
       </c>
       <c r="L73" t="n">
         <v>2.7</v>
@@ -4602,7 +5477,7 @@
         <v>0.86</v>
       </c>
       <c r="N73" t="n">
-        <v>1.36</v>
+        <v>4.62</v>
       </c>
       <c r="O73" t="n">
         <v>-2.37</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>6.79</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46289.38541666666</v>
+        <v>46289.55208333334</v>
       </c>
       <c r="H74" t="n">
-        <v>17311</v>
+        <v>17153</v>
       </c>
       <c r="I74" t="n">
         <v>17211.50163205015</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.97</v>
+        <v>-4.85</v>
       </c>
       <c r="L74" t="n">
-        <v>4.69</v>
+        <v>5.08</v>
       </c>
       <c r="M74" t="n">
         <v>1.05</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>4.47</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46309.55208333334</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>17240</v>
+        <v>17680</v>
       </c>
       <c r="I75" t="n">
         <v>17501.80745621724</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.51</v>
+        <v>-3.07</v>
       </c>
       <c r="L75" t="n">
-        <v>1.64</v>
+        <v>3.92</v>
       </c>
       <c r="M75" t="n">
         <v>1.28</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>6.5</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46316.38541666666</v>
+        <v>46316.55208333334</v>
       </c>
       <c r="H76" t="n">
-        <v>16869</v>
+        <v>16820</v>
       </c>
       <c r="I76" t="n">
         <v>16840.11049083951</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K76" t="n">
-        <v>-4.59</v>
+        <v>-4.86</v>
       </c>
       <c r="L76" t="n">
-        <v>4.69</v>
+        <v>5.16</v>
       </c>
       <c r="M76" t="n">
         <v>0.17</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4833,6 +5756,12 @@
       <c r="Q77" t="n">
         <v>9</v>
       </c>
+      <c r="R77" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6833,7 +7762,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.7</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="6">
@@ -6843,7 +7772,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.2</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="7">
@@ -6853,7 +7782,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8">
@@ -6863,7 +7792,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6873,7 +7802,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.1</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="10">
@@ -6883,7 +7812,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="11">
@@ -6893,7 +7822,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -6903,7 +7832,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -6913,7 +7842,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>82.7</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="14">
@@ -6923,7 +7852,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.34</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="15">
@@ -6933,7 +7862,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.78</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="16">
@@ -6943,7 +7872,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.82</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="17">
@@ -6953,7 +7882,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>110.54</v>
+        <v>108.84</v>
       </c>
     </row>
     <row r="18">
@@ -6963,7 +7892,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -6973,7 +7902,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.44</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="20">
@@ -6983,7 +7912,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.8</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="21">
@@ -6993,7 +7922,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.59</v>
+        <v>22.13</v>
       </c>
     </row>
     <row r="22">
@@ -7003,7 +7932,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -7013,7 +7942,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
@@ -7023,7 +7952,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.36</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="25">
@@ -7033,7 +7962,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.64</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="26">
@@ -7043,7 +7972,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.35</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="27">
@@ -7053,7 +7982,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.94</v>
+        <v>31.46</v>
       </c>
     </row>
     <row r="28">
@@ -7063,7 +7992,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29">
